--- a/reports/result.xlsx
+++ b/reports/result.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Module</t>
   </si>
@@ -28,16 +28,37 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>Login with valid credentials</t>
-  </si>
-  <si>
-    <t>16.25</t>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Dashboard Verified</t>
+  </si>
+  <si>
+    <t>0.04</t>
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Profile Icon Clicked</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>Navigated back to previous page</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>Notification Icon Clicked</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>0.08</t>
   </si>
 </sst>
 </file>
@@ -414,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -458,6 +479,74 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
